--- a/outputs/portfolio_combined/cumulative_returns.xlsx
+++ b/outputs/portfolio_combined/cumulative_returns.xlsx
@@ -1032,7 +1032,7 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0.9996494839311575</v>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
@@ -1055,7 +1055,7 @@
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>1.000376899718427</v>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
@@ -1078,7 +1078,7 @@
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>1.001050324551129</v>
+        <v>1.004174123851959</v>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
@@ -1101,7 +1101,7 @@
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>1.001101468950007</v>
+        <v>1.007100431649926</v>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
@@ -1124,7 +1124,7 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>1.001101468950007</v>
+        <v>1.003867304387971</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
@@ -1147,7 +1147,7 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>1.003533460023798</v>
+        <v>1.008012438198472</v>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
@@ -1170,7 +1170,7 @@
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>1.003533460023798</v>
+        <v>1.006955127113014</v>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
@@ -1193,7 +1193,7 @@
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>1.004970477349056</v>
+        <v>1.013229152176703</v>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
@@ -1216,7 +1216,7 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>1.006747918276342</v>
+        <v>1.016772974683907</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
@@ -1239,7 +1239,7 @@
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>1.006769742444945</v>
+        <v>1.019162426065321</v>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
@@ -1262,7 +1262,7 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>1.007154537225279</v>
+        <v>1.022279692242275</v>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
@@ -1285,7 +1285,7 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>1.007671611305419</v>
+        <v>1.023240403212871</v>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
@@ -1308,7 +1308,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>1.007671611305419</v>
+        <v>1.028830044476092</v>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
@@ -1331,7 +1331,7 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>1.007671611305419</v>
+        <v>1.029846316398948</v>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
@@ -1354,7 +1354,7 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>1.006276173996477</v>
+        <v>1.029343521096091</v>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
@@ -1377,7 +1377,7 @@
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="n">
-        <v>1.006276173996477</v>
+        <v>1.030415774160722</v>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
@@ -1400,7 +1400,7 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>1.006276173996477</v>
+        <v>1.030990134844183</v>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
@@ -1423,7 +1423,7 @@
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>1.005092891251268</v>
+        <v>1.027706851070151</v>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
@@ -1446,7 +1446,7 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>1.005092891251268</v>
+        <v>1.030508997788635</v>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
@@ -1469,7 +1469,7 @@
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>1.005092891251268</v>
+        <v>1.027736867265369</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
@@ -1492,7 +1492,7 @@
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>1.00235139834577</v>
+        <v>1.026779983773037</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
@@ -1515,7 +1515,7 @@
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>1.004830449376814</v>
+        <v>1.030764026937578</v>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
@@ -1538,7 +1538,7 @@
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>1.005298838856018</v>
+        <v>1.029318418524181</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -1561,7 +1561,7 @@
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>1.003011622401323</v>
+        <v>1.028832528141512</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
@@ -1584,7 +1584,7 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>1.008930262474264</v>
+        <v>1.035976606907534</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
@@ -1607,7 +1607,7 @@
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>1.008930262474264</v>
+        <v>1.036339480757128</v>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
@@ -1630,7 +1630,7 @@
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>1.009023477040455</v>
+        <v>1.040951200830642</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
@@ -1653,7 +1653,7 @@
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>1.009023477040455</v>
+        <v>1.042473722002915</v>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
@@ -1676,7 +1676,7 @@
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>1.009023477040455</v>
+        <v>1.040367507592985</v>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
@@ -1699,7 +1699,7 @@
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>1.009983873994697</v>
+        <v>1.041526159812716</v>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
@@ -1722,7 +1722,7 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>1.009983873994697</v>
+        <v>1.03748281945765</v>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
@@ -1745,7 +1745,7 @@
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>1.009983873994697</v>
+        <v>1.034117526465729</v>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
@@ -1768,7 +1768,7 @@
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>1.011985213176453</v>
+        <v>1.039549489480372</v>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
@@ -1791,7 +1791,7 @@
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>1.011985213176453</v>
+        <v>1.03909392230311</v>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
@@ -1814,7 +1814,7 @@
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>1.011985213176453</v>
+        <v>1.036414144610947</v>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
@@ -1837,7 +1837,7 @@
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="n">
-        <v>1.00916027527953</v>
+        <v>1.026614708478144</v>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
@@ -1860,7 +1860,7 @@
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>1.00916027527953</v>
+        <v>1.028266189568575</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
@@ -1883,7 +1883,7 @@
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>1.00916027527953</v>
+        <v>1.036869937531822</v>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
@@ -1906,7 +1906,7 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>1.009392546170633</v>
+        <v>1.038947930369224</v>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
@@ -1929,7 +1929,7 @@
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="n">
-        <v>1.009392546170633</v>
+        <v>1.039772425279752</v>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
@@ -1952,7 +1952,7 @@
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>1.009392546170633</v>
+        <v>1.034890006425518</v>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
@@ -1975,7 +1975,7 @@
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>1.011988152750749</v>
+        <v>1.041305465343968</v>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
@@ -1998,7 +1998,7 @@
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="n">
-        <v>1.011988152750749</v>
+        <v>1.044228896565238</v>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
@@ -2021,7 +2021,7 @@
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>1.011988152750749</v>
+        <v>1.045141539345163</v>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
@@ -2044,7 +2044,7 @@
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>1.011108633396116</v>
+        <v>1.043499612638323</v>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
@@ -2067,7 +2067,7 @@
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
-        <v>1.011108633396116</v>
+        <v>1.046834949111859</v>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
@@ -2090,7 +2090,7 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="n">
-        <v>1.011108633396116</v>
+        <v>1.051001286818688</v>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
@@ -2113,7 +2113,7 @@
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="n">
-        <v>1.012791806071955</v>
+        <v>1.055957221748249</v>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
@@ -2136,7 +2136,7 @@
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="n">
-        <v>1.013425554404035</v>
+        <v>1.061413392858017</v>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
@@ -2159,7 +2159,7 @@
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="n">
-        <v>1.013425554404035</v>
+        <v>1.06373214606086</v>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
@@ -2182,7 +2182,7 @@
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>1.014162972698035</v>
+        <v>1.065807007873883</v>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
@@ -2205,7 +2205,7 @@
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>1.014651927913693</v>
+        <v>1.06975529739892</v>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
@@ -2228,7 +2228,7 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>1.014651927913693</v>
+        <v>1.070417547175866</v>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
@@ -2251,7 +2251,7 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>1.015496788410756</v>
+        <v>1.075637431535647</v>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
@@ -2274,7 +2274,7 @@
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="n">
-        <v>1.015845870566036</v>
+        <v>1.076719702199887</v>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
@@ -2297,7 +2297,7 @@
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>1.016806980168487</v>
+        <v>1.081165985592252</v>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
@@ -2320,7 +2320,7 @@
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>1.017736680374513</v>
+        <v>1.08187121365491</v>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
@@ -2343,7 +2343,7 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>1.020476494898159</v>
+        <v>1.083531510224543</v>
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
@@ -2366,7 +2366,7 @@
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="n">
-        <v>1.020470341833692</v>
+        <v>1.083941424617834</v>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
@@ -2389,7 +2389,7 @@
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="n">
-        <v>1.022057458595951</v>
+        <v>1.08894467325992</v>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
@@ -2412,7 +2412,7 @@
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>1.022057458595951</v>
+        <v>1.085713885027693</v>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="n">
-        <v>1.022057458595951</v>
+        <v>1.083058605575347</v>
       </c>
       <c r="F99" t="n">
         <v>0.9820285658175975</v>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
-        <v>1.021453391465537</v>
+        <v>1.08317315725035</v>
       </c>
       <c r="F100" t="n">
         <v>0.9667129124926984</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="n">
-        <v>1.021453391465537</v>
+        <v>1.081880232530944</v>
       </c>
       <c r="F101" t="n">
         <v>0.9191172876324502</v>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="n">
-        <v>1.021453391465537</v>
+        <v>1.082425429791593</v>
       </c>
       <c r="F102" t="n">
         <v>0.933023050458757</v>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="n">
-        <v>1.022325755318236</v>
+        <v>1.083177157225143</v>
       </c>
       <c r="F103" t="n">
         <v>0.9383988017638679</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="n">
-        <v>1.022325755318236</v>
+        <v>1.082555065888398</v>
       </c>
       <c r="F104" t="n">
         <v>0.9289869899884347</v>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="n">
-        <v>1.022325755318236</v>
+        <v>1.083062014307215</v>
       </c>
       <c r="F105" t="n">
         <v>0.9420936072280045</v>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
-        <v>1.020867942064798</v>
+        <v>1.074886496392228</v>
       </c>
       <c r="F106" t="n">
         <v>1.003048890602674</v>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="n">
-        <v>1.020867942064798</v>
+        <v>1.074067709137815</v>
       </c>
       <c r="F107" t="n">
         <v>1.043656282065516</v>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="n">
-        <v>1.020867942064798</v>
+        <v>1.066585604352737</v>
       </c>
       <c r="F108" t="n">
         <v>1.080857714822802</v>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="n">
-        <v>1.023618906511051</v>
+        <v>1.076981620620544</v>
       </c>
       <c r="F109" t="n">
         <v>0.9885147072279475</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="n">
-        <v>1.023618906511051</v>
+        <v>1.083100330188015</v>
       </c>
       <c r="F110" t="n">
         <v>0.9585009371818075</v>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="n">
-        <v>1.024824329394689</v>
+        <v>1.082417483149975</v>
       </c>
       <c r="F111" t="n">
         <v>0.9642027600677622</v>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="n">
-        <v>1.026262800744361</v>
+        <v>1.086088671880511</v>
       </c>
       <c r="F112" t="n">
         <v>0.9287842406548498</v>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="n">
-        <v>1.026262800744361</v>
+        <v>1.078032013493663</v>
       </c>
       <c r="F113" t="n">
         <v>1.015927129057864</v>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="n">
-        <v>1.026262800744361</v>
+        <v>1.08546755609103</v>
       </c>
       <c r="F114" t="n">
         <v>0.9637256893502353</v>
@@ -2869,7 +2869,7 @@
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="n">
-        <v>1.02652082353377</v>
+        <v>1.088305263935609</v>
       </c>
       <c r="F115" t="n">
         <v>0.9481952497575612</v>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="n">
-        <v>1.02652082353377</v>
+        <v>1.083943932753624</v>
       </c>
       <c r="F116" t="n">
         <v>1.014708843486599</v>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="n">
-        <v>1.02652082353377</v>
+        <v>1.089017636019198</v>
       </c>
       <c r="F117" t="n">
         <v>1.012227058195229</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="n">
-        <v>1.02744784126759</v>
+        <v>1.091563272340384</v>
       </c>
       <c r="F118" t="n">
         <v>0.9844390963560179</v>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="n">
-        <v>1.02744784126759</v>
+        <v>1.095957573336823</v>
       </c>
       <c r="F119" t="n">
         <v>0.9235370309698631</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="n">
-        <v>1.02744784126759</v>
+        <v>1.099361245737068</v>
       </c>
       <c r="F120" t="n">
         <v>0.8863097682018357</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="n">
-        <v>1.027484063238546</v>
+        <v>1.099797365165193</v>
       </c>
       <c r="F121" t="n">
         <v>0.9288984307335478</v>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="n">
-        <v>1.027484063238546</v>
+        <v>1.088953707161604</v>
       </c>
       <c r="F122" t="n">
         <v>0.9098726720613973</v>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="n">
-        <v>1.027484063238546</v>
+        <v>1.070516585975694</v>
       </c>
       <c r="F123" t="n">
         <v>0.9956529766491691</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>1.0299613560249</v>
+        <v>1.089087963689946</v>
       </c>
       <c r="F124" t="n">
         <v>0.7888796222745447</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="n">
-        <v>1.0299613560249</v>
+        <v>1.096513965460779</v>
       </c>
       <c r="F125" t="n">
         <v>0.7592407930949728</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="n">
-        <v>1.035404416971588</v>
+        <v>1.102853404631532</v>
       </c>
       <c r="F126" t="n">
         <v>0.7116791416109906</v>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="n">
-        <v>1.040073497403415</v>
+        <v>1.108357218071754</v>
       </c>
       <c r="F127" t="n">
         <v>0.7094220386199687</v>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="n">
-        <v>1.040073497403415</v>
+        <v>1.113331937168366</v>
       </c>
       <c r="F128" t="n">
         <v>0.6532164223577392</v>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="n">
-        <v>1.040073497403415</v>
+        <v>1.110495966201879</v>
       </c>
       <c r="F129" t="n">
         <v>0.6785818710682996</v>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="n">
-        <v>1.038767053939845</v>
+        <v>1.107414186392563</v>
       </c>
       <c r="F130" t="n">
         <v>0.6606655987469086</v>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="n">
-        <v>1.038767053939845</v>
+        <v>1.127768454227093</v>
       </c>
       <c r="F131" t="n">
         <v>0.5222061665699201</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="n">
-        <v>1.038767053939845</v>
+        <v>1.133768080367769</v>
       </c>
       <c r="F132" t="n">
         <v>0.4787302321075739</v>
@@ -3355,7 +3355,7 @@
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="n">
-        <v>1.038218869500335</v>
+        <v>1.134880350598312</v>
       </c>
       <c r="F133" t="n">
         <v>0.4635672825186095</v>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="n">
-        <v>1.038218869500335</v>
+        <v>1.142134666647318</v>
       </c>
       <c r="F134" t="n">
         <v>0.3862827554344724</v>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="n">
-        <v>1.038218869500335</v>
+        <v>1.147561831016326</v>
       </c>
       <c r="F135" t="n">
         <v>0.4094932291799868</v>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="n">
-        <v>1.038702043042325</v>
+        <v>1.149927717031529</v>
       </c>
       <c r="F136" t="n">
         <v>0.412915666725341</v>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="n">
-        <v>1.038702043042325</v>
+        <v>1.154096901381382</v>
       </c>
       <c r="F137" t="n">
         <v>0.403842844506216</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="n">
-        <v>1.038702043042325</v>
+        <v>1.152991445159967</v>
       </c>
       <c r="F138" t="n">
         <v>0.4030189488060119</v>
@@ -3517,7 +3517,7 @@
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="n">
-        <v>1.039257553857512</v>
+        <v>1.149100508297145</v>
       </c>
       <c r="F139" t="n">
         <v>0.4315890136467309</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="n">
-        <v>1.039257553857512</v>
+        <v>1.153086218167508</v>
       </c>
       <c r="F140" t="n">
         <v>0.4246321326106224</v>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="n">
-        <v>1.039257553857512</v>
+        <v>1.150007248222656</v>
       </c>
       <c r="F141" t="n">
         <v>0.3955037702528861</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="n">
-        <v>1.041026084661623</v>
+        <v>1.150476135919106</v>
       </c>
       <c r="F142" t="n">
         <v>0.3915564893484152</v>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
-        <v>1.041026084661623</v>
+        <v>1.145223824707222</v>
       </c>
       <c r="F143" t="n">
         <v>0.4040986723342181</v>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="n">
-        <v>1.041026084661623</v>
+        <v>1.153220570084141</v>
       </c>
       <c r="F144" t="n">
         <v>0.420823881432537</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="n">
-        <v>1.039210595205461</v>
+        <v>1.150003311710692</v>
       </c>
       <c r="F145" t="n">
         <v>0.41532871017287</v>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="n">
-        <v>1.039210595205461</v>
+        <v>1.14718204592638</v>
       </c>
       <c r="F146" t="n">
         <v>0.4053090318817222</v>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="n">
-        <v>1.039210595205461</v>
+        <v>1.150913335647259</v>
       </c>
       <c r="F147" t="n">
         <v>0.4105753368895815</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="n">
-        <v>1.038106576973264</v>
+        <v>1.143370583817722</v>
       </c>
       <c r="F148" t="n">
         <v>0.4378047653790728</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="n">
-        <v>1.038106576973264</v>
+        <v>1.145009263498874</v>
       </c>
       <c r="F149" t="n">
         <v>0.4134717217609134</v>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="n">
-        <v>1.038106576973264</v>
+        <v>1.131587040223139</v>
       </c>
       <c r="F150" t="n">
         <v>0.4654789626752402</v>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="n">
-        <v>1.040560477205542</v>
+        <v>1.143554035931176</v>
       </c>
       <c r="F151" t="n">
         <v>0.4283930589527856</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="n">
-        <v>1.040560477205542</v>
+        <v>1.139841124869379</v>
       </c>
       <c r="F152" t="n">
         <v>0.4242938041503735</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="n">
-        <v>1.040560477205542</v>
+        <v>1.130382814072396</v>
       </c>
       <c r="F153" t="n">
         <v>0.4337851375036025</v>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="n">
-        <v>1.044207681206458</v>
+        <v>1.148099320907058</v>
       </c>
       <c r="F154" t="n">
         <v>0.3935667721386672</v>
@@ -3949,7 +3949,7 @@
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="n">
-        <v>1.044207681206458</v>
+        <v>1.161776759271594</v>
       </c>
       <c r="F155" t="n">
         <v>0.3721416305411537</v>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="n">
-        <v>1.044207681206458</v>
+        <v>1.159328195026089</v>
       </c>
       <c r="F156" t="n">
         <v>0.3848867821530751</v>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="n">
-        <v>1.047298802505251</v>
+        <v>1.174968686564731</v>
       </c>
       <c r="F157" t="n">
         <v>0.3337931710743545</v>
@@ -4030,7 +4030,7 @@
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="n">
-        <v>1.047298802505251</v>
+        <v>1.173106871124026</v>
       </c>
       <c r="F158" t="n">
         <v>0.3293424327343205</v>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="n">
-        <v>1.047298802505251</v>
+        <v>1.172921759770256</v>
       </c>
       <c r="F159" t="n">
         <v>0.3463539683152754</v>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="n">
-        <v>1.048238807945606</v>
+        <v>1.171531250976751</v>
       </c>
       <c r="F160" t="n">
         <v>0.3637908539809438</v>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="n">
-        <v>1.048238807945606</v>
+        <v>1.168874291944762</v>
       </c>
       <c r="F161" t="n">
         <v>0.3486918856337192</v>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="n">
-        <v>1.048238807945606</v>
+        <v>1.176134609711375</v>
       </c>
       <c r="F162" t="n">
         <v>0.321972717541147</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="n">
-        <v>1.049214627200111</v>
+        <v>1.182065051499614</v>
       </c>
       <c r="F163" t="n">
         <v>0.2964487821470294</v>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="n">
-        <v>1.049214627200111</v>
+        <v>1.178773639818878</v>
       </c>
       <c r="F164" t="n">
         <v>0.3043877843156901</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="n">
-        <v>1.049214627200111</v>
+        <v>1.17169560166825</v>
       </c>
       <c r="F165" t="n">
         <v>0.3115912056873976</v>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="n">
-        <v>1.047002238957381</v>
+        <v>1.161457522006697</v>
       </c>
       <c r="F166" t="n">
         <v>0.3387298719691476</v>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="n">
-        <v>1.047501436012402</v>
+        <v>1.174725241834639</v>
       </c>
       <c r="F167" t="n">
         <v>0.3128616505521238</v>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="n">
-        <v>1.051824948004119</v>
+        <v>1.178678311141303</v>
       </c>
       <c r="F168" t="n">
         <v>0.3004334581112389</v>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="n">
-        <v>1.052417749573544</v>
+        <v>1.178833734020506</v>
       </c>
       <c r="F169" t="n">
         <v>0.3055527641735201</v>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="n">
-        <v>1.052417749573544</v>
+        <v>1.18067865812558</v>
       </c>
       <c r="F170" t="n">
         <v>0.2987740720503571</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="n">
-        <v>1.052417749573544</v>
+        <v>1.183732135317818</v>
       </c>
       <c r="F171" t="n">
         <v>0.2938967152604414</v>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="n">
-        <v>1.051379935617219</v>
+        <v>1.17916460096154</v>
       </c>
       <c r="F172" t="n">
         <v>0.3001179331543952</v>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="n">
-        <v>1.051379935617219</v>
+        <v>1.181020631102739</v>
       </c>
       <c r="F173" t="n">
         <v>0.2988743474625273</v>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="n">
-        <v>1.051379935617219</v>
+        <v>1.181517810070274</v>
       </c>
       <c r="F174" t="n">
         <v>0.2991714077543712</v>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="n">
-        <v>1.051546687889312</v>
+        <v>1.180586667354671</v>
       </c>
       <c r="F175" t="n">
         <v>0.3059610686763482</v>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="n">
-        <v>1.051546687889312</v>
+        <v>1.184919500520293</v>
       </c>
       <c r="F176" t="n">
         <v>0.3229345559171523</v>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="n">
-        <v>1.051546687889312</v>
+        <v>1.188116882085837</v>
       </c>
       <c r="F177" t="n">
         <v>0.3184501208976787</v>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="n">
-        <v>1.048527784739788</v>
+        <v>1.18430967498528</v>
       </c>
       <c r="F178" t="n">
         <v>0.317082845841251</v>
@@ -4597,7 +4597,7 @@
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="n">
-        <v>1.048527784739788</v>
+        <v>1.184915427660396</v>
       </c>
       <c r="F179" t="n">
         <v>0.3007530268133237</v>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="n">
-        <v>1.048527784739788</v>
+        <v>1.181167621813177</v>
       </c>
       <c r="F180" t="n">
         <v>0.2949899876579826</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="n">
-        <v>1.048435485181289</v>
+        <v>1.185999009702417</v>
       </c>
       <c r="F181" t="n">
         <v>0.2921030810538308</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="n">
-        <v>1.048435485181289</v>
+        <v>1.186721625511874</v>
       </c>
       <c r="F182" t="n">
         <v>0.3008427407717193</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="n">
-        <v>1.048435485181289</v>
+        <v>1.184570433284465</v>
       </c>
       <c r="F183" t="n">
         <v>0.3210590237485509</v>
